--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_deviation_monitoring/deviation_monitoring/dsas_g11_bearings_vibration_temp_deviation_monitoring_output4.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_deviation_monitoring/deviation_monitoring/dsas_g11_bearings_vibration_temp_deviation_monitoring_output4.xlsx
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.0001650629716247504</v>
+        <v>6.552718977789746e-05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.0001282458073983798</v>
+        <v>1.711923162899281e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.0001038091292586319</v>
+        <v>1.291224106758609e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.0001038091292586319</v>
+        <v>1.291224106758609e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.0001038091292586319</v>
+        <v>1.291224106758609e-05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.0001274548948948813</v>
+        <v>2.390760723689303e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.000396044852549792</v>
+        <v>0.0001682185838600226</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.0002565618516955629</v>
+        <v>9.695238677779049e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.0001449828893366937</v>
+        <v>8.522364517810608e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.0001690967790403728</v>
+        <v>8.220168751594937e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.000588675202228574</v>
+        <v>0.0001035126449398262</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.0003028269614599201</v>
+        <v>4.807230615358263e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>6.904298224001225e-05</v>
+        <v>8.971835009922009e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.0001769748027437198</v>
+        <v>7.32560962225668e-05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.0003290759409800839</v>
+        <v>8.037483699916526e-05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.0004949917123500092</v>
+        <v>8.566660519499364e-05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.0003476108599956193</v>
+        <v>8.354234488406736e-05</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.0005234690394343362</v>
+        <v>0.0001671759291778641</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.0002609219746960572</v>
+        <v>6.156987951255655e-05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.0004431369795292316</v>
+        <v>0.0001014683681317722</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.0006280117316161045</v>
+        <v>0.0002014502434177423</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.0008009131258601378</v>
+        <v>0.0001138816797212861</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.0003730869143174794</v>
+        <v>8.64218031539071e-05</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.0002676573020333387</v>
+        <v>5.386990429203449e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.0003125039938352174</v>
+        <v>7.184072636287712e-05</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.0003125039938352174</v>
+        <v>7.184072636287712e-05</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>9.489074659752182e-05</v>
+        <v>6.893588009842735e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.0002245093771487564</v>
+        <v>0.000121138406213379</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.0002295523866457585</v>
+        <v>0.0001281366823526891</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.0007541493697546014</v>
+        <v>7.668301492153273e-05</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.0005392423993771914</v>
+        <v>5.558454420614758e-05</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.0007932030022600781</v>
+        <v>9.962112625031866e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.0003356581495107504</v>
+        <v>5.52049942451495e-05</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.0001270268851551765</v>
+        <v>0.000109404566293473</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R35" t="b">
         <v>0</v>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.0003157726184980314</v>
+        <v>8.08614215189863e-05</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.0002186020401380601</v>
+        <v>7.20753239104716e-05</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.0002959644670801564</v>
+        <v>5.541317553576343e-05</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.0001350026560627546</v>
+        <v>4.473061335854358e-05</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.0006483118516788168</v>
+        <v>6.153812853972924e-05</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.0003092357475760841</v>
+        <v>0.0002475639360302477</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.0006840073787316484</v>
+        <v>7.578104281071327e-05</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.000927693869006956</v>
+        <v>7.506881050682436e-05</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.001643588797919302</v>
+        <v>9.482980092006063e-05</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.0008255605166711077</v>
+        <v>5.227567125487641e-05</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.0005310960679350102</v>
+        <v>4.920796490473619e-05</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.000300444918375946</v>
+        <v>0.0001627663420540346</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.001738051697321747</v>
+        <v>8.373806621317419e-05</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.0003238664574990972</v>
+        <v>7.532867275910665e-05</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.0002206678489567808</v>
+        <v>0.000104269783346335</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R50" t="b">
         <v>0</v>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.0002185735593897551</v>
+        <v>0.0001286766881620421</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0.0002021748917940528</v>
+        <v>6.84854377808143e-05</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.0004268661153378966</v>
+        <v>7.955279865215662e-05</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R53" t="b">
         <v>0</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.0004616884136660927</v>
+        <v>8.30672678481663e-05</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.0004279050622528667</v>
+        <v>7.140409421740997e-05</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.0002708376299280665</v>
+        <v>7.301401255743344e-05</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R56" t="b">
         <v>0</v>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.0002708376299280665</v>
+        <v>7.301401255743344e-05</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.001003009592368644</v>
+        <v>6.669411371606584e-05</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.0007793390668134527</v>
+        <v>7.800823508821807e-05</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R59" t="b">
         <v>0</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.0006493384151890434</v>
+        <v>9.164277724055015e-05</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
@@ -4295,17 +4295,17 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.03611817002915319</v>
+        <v>0.0005899209535732727</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>⚠️ Anomaly</t>
+          <t>✅ Normal</t>
         </is>
       </c>
     </row>
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.0005819969284897071</v>
+        <v>0.0001092509255288292</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R62" t="b">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.08147537342164443</v>
+        <v>0.08007846046114765</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R63" t="b">
         <v>1</v>
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0.0001374002864790918</v>
+        <v>0.0001077849939819551</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.0001189134786242165</v>
+        <v>0.0001054041878268477</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R65" t="b">
         <v>0</v>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.0006191199791668951</v>
+        <v>6.065868645189842e-05</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
@@ -4673,17 +4673,17 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.04054678806025536</v>
+        <v>0.001091456981094991</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>⚠️ Anomaly</t>
+          <t>✅ Normal</t>
         </is>
       </c>
     </row>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.0004495654984972037</v>
+        <v>7.831469035582246e-05</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R68" t="b">
         <v>0</v>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.0002602123424743556</v>
+        <v>6.181535794347783e-05</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0.0007260341711420873</v>
+        <v>7.870373217170882e-05</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.0007270567448777149</v>
+        <v>8.99280428811871e-05</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R71" t="b">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.0006340580424334905</v>
+        <v>8.096310610243815e-05</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.0007317965645984977</v>
+        <v>9.969374803755648e-05</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
@@ -5114,10 +5114,10 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.0006837184708586331</v>
+        <v>0.0001208876734373585</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R74" t="b">
         <v>0</v>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.0003729858188728956</v>
+        <v>7.950010623806149e-05</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R75" t="b">
         <v>0</v>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.0003313360604157957</v>
+        <v>0.0001011376107088191</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R76" t="b">
         <v>0</v>
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.0006484806368534112</v>
+        <v>9.388575909098884e-05</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0.0003035365678582868</v>
+        <v>0.0001278931760236082</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R78" t="b">
         <v>0</v>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.0002901464617599734</v>
+        <v>0.0001125118893863838</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R79" t="b">
         <v>0</v>
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.000663821063808018</v>
+        <v>0.0001135281621849081</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R80" t="b">
         <v>0</v>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0.0005162017886847115</v>
+        <v>5.639527784233135e-05</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R81" t="b">
         <v>0</v>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0.0002538467216514671</v>
+        <v>8.498163086480669e-05</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
@@ -5681,10 +5681,10 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.001357885914720756</v>
+        <v>0.0001290022981363016</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R83" t="b">
         <v>0</v>
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0.0004832438396359092</v>
+        <v>9.734910946223914e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R84" t="b">
         <v>0</v>
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.0004731199733503053</v>
+        <v>9.778043213041225e-05</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R85" t="b">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.00196161861006415</v>
+        <v>0.0002953217918623244</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R86" t="b">
         <v>0</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.01194901522128504</v>
+        <v>0.0100157725333895</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R87" t="b">
         <v>0</v>
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0.000679898156846987</v>
+        <v>0.0001272831665800935</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R88" t="b">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.000679898156846987</v>
+        <v>0.0001272831665800935</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R89" t="b">
         <v>0</v>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0.001302448747873144</v>
+        <v>7.998290321118299e-05</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R90" t="b">
         <v>0</v>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0.001365208774526233</v>
+        <v>7.995237615634218e-05</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R91" t="b">
         <v>0</v>
@@ -6248,10 +6248,10 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0.001567105209862109</v>
+        <v>9.084417702485741e-05</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R92" t="b">
         <v>0</v>
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.001201171572758532</v>
+        <v>9.652588431431813e-05</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
@@ -6374,10 +6374,10 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.0003934588136643909</v>
+        <v>0.000146429512147804</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R94" t="b">
         <v>0</v>
@@ -6437,10 +6437,10 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0.001508249952031808</v>
+        <v>0.0001031673749753137</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R95" t="b">
         <v>0</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0.001406440683777313</v>
+        <v>4.744803853959281e-05</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R96" t="b">
         <v>0</v>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.0007957121285369771</v>
+        <v>0.0001170802040146082</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
@@ -6626,10 +6626,10 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0.0005423214699734733</v>
+        <v>6.249406534523004e-05</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.0004480218195862261</v>
+        <v>5.308197928804528e-05</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R99" t="b">
         <v>0</v>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.0005207153834070511</v>
+        <v>7.549350036629376e-05</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R100" t="b">
         <v>0</v>
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0.0005207153834070511</v>
+        <v>7.549350036629376e-05</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R101" t="b">
         <v>0</v>
@@ -6878,10 +6878,10 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0.0004032458703979514</v>
+        <v>5.486340191209401e-05</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R102" t="b">
         <v>0</v>
@@ -6941,10 +6941,10 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.0004746126494041499</v>
+        <v>8.317694698609575e-05</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R103" t="b">
         <v>0</v>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0.0004746126494041499</v>
+        <v>8.317694698609575e-05</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R104" t="b">
         <v>0</v>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0.0002971620862544661</v>
+        <v>4.531987942559623e-05</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R105" t="b">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0.0003179885031605076</v>
+        <v>3.691334722190089e-05</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R106" t="b">
         <v>0</v>
@@ -7193,10 +7193,10 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0.00171448471944753</v>
+        <v>9.638602831196015e-05</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R107" t="b">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0.0005676639106175933</v>
+        <v>4.912235370054025e-05</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R108" t="b">
         <v>0</v>
@@ -7319,10 +7319,10 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0.000496513799900867</v>
+        <v>7.301793409544635e-05</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R109" t="b">
         <v>0</v>
@@ -7382,10 +7382,10 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0.000627155231678542</v>
+        <v>8.730575100078634e-05</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R110" t="b">
         <v>0</v>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0.0002748477294147639</v>
+        <v>5.050919692697965e-05</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R111" t="b">
         <v>0</v>
@@ -7508,10 +7508,10 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0.0003710862781881629</v>
+        <v>2.900973532908977e-05</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R112" t="b">
         <v>0</v>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0.002541929920645053</v>
+        <v>0.000158230998628987</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R113" t="b">
         <v>0</v>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0.000566805208016777</v>
+        <v>4.607219834879523e-05</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R114" t="b">
         <v>0</v>
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0.0005075301446929493</v>
+        <v>0.0003969156003155648</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R115" t="b">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0.0002521733257482319</v>
+        <v>0.0001346005513609456</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R116" t="b">
         <v>0</v>
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0.0005195224128493556</v>
+        <v>7.825824104910187e-05</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R117" t="b">
         <v>0</v>
@@ -7886,10 +7886,10 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0.0009846614972564512</v>
+        <v>4.834003129345142e-05</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R118" t="b">
         <v>0</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0.001096099410000464</v>
+        <v>7.0474441025885e-05</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R119" t="b">
         <v>0</v>
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0.0008650095320063945</v>
+        <v>4.804985771771875e-05</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R120" t="b">
         <v>0</v>
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0.0006267188459384596</v>
+        <v>9.750388092800801e-05</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R121" t="b">
         <v>0</v>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0.01224676738182557</v>
+        <v>0.001237160066885666</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R122" t="b">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0.0004794643343699043</v>
+        <v>5.418301188858927e-05</v>
       </c>
       <c r="Q123" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R123" t="b">
         <v>0</v>
@@ -8264,10 +8264,10 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0.001207226761817206</v>
+        <v>0.0001685648616236126</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R124" t="b">
         <v>0</v>
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0.001167234288868076</v>
+        <v>7.138380264279132e-05</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R125" t="b">
         <v>0</v>
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0.0005646430216582348</v>
+        <v>7.020382288595095e-05</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R126" t="b">
         <v>0</v>
@@ -8453,10 +8453,10 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0.0004469137336996325</v>
+        <v>0.0001220860549593409</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R127" t="b">
         <v>0</v>
@@ -8516,10 +8516,10 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0.0004469137336996325</v>
+        <v>0.0001220860549593409</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R128" t="b">
         <v>0</v>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0.0005847908175410247</v>
+        <v>4.503973293980687e-05</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R129" t="b">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0.0007392860335534556</v>
+        <v>3.915411854274608e-05</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R130" t="b">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0.001980203302373253</v>
+        <v>0.0001003214125638958</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R131" t="b">
         <v>0</v>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0.0007289052993600721</v>
+        <v>7.55964598447289e-05</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R132" t="b">
         <v>0</v>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0.0005732805996705663</v>
+        <v>6.025202011769871e-05</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R133" t="b">
         <v>0</v>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0.0005084874206594925</v>
+        <v>6.422390325519216e-05</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R134" t="b">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0.004517985531371679</v>
+        <v>0.004186984992314137</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R135" t="b">
         <v>0</v>
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0.0004361024621220265</v>
+        <v>6.040977550823392e-05</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R136" t="b">
         <v>0</v>
@@ -9083,10 +9083,10 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0.001815660899362329</v>
+        <v>9.934842337371896e-05</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R137" t="b">
         <v>0</v>
@@ -9146,10 +9146,10 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0.0006488368917227923</v>
+        <v>5.075873625894007e-05</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R138" t="b">
         <v>0</v>
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0.0004208811397250757</v>
+        <v>6.225043530082693e-05</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R139" t="b">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0.000346241853023093</v>
+        <v>4.640564736669959e-05</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R140" t="b">
         <v>0</v>
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0.0003835397280531453</v>
+        <v>6.442832114682808e-05</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R141" t="b">
         <v>0</v>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0.001918773954310087</v>
+        <v>4.902075312776836e-05</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R142" t="b">
         <v>0</v>
@@ -9461,10 +9461,10 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0.001881319710787982</v>
+        <v>9.673810933637841e-05</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R143" t="b">
         <v>0</v>
@@ -9524,10 +9524,10 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0.000371655385238488</v>
+        <v>4.58445917285745e-05</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R144" t="b">
         <v>0</v>
@@ -9587,10 +9587,10 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0.0002270704722427873</v>
+        <v>4.053227006685459e-05</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R145" t="b">
         <v>0</v>
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0.0004889046066913793</v>
+        <v>9.035738463546514e-05</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R146" t="b">
         <v>0</v>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0.0006989430406073748</v>
+        <v>0.000110545138938062</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R147" t="b">
         <v>0</v>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0.0004122025097807443</v>
+        <v>9.296116735605755e-05</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R148" t="b">
         <v>0</v>
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0.004233555813782063</v>
+        <v>0.0001382931999184515</v>
       </c>
       <c r="Q149" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R149" t="b">
         <v>0</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0.008020803391660546</v>
+        <v>0.006182201726926434</v>
       </c>
       <c r="Q150" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R150" t="b">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0.0004672387369878799</v>
+        <v>8.522237594269132e-05</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R151" t="b">
         <v>0</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0.0006110824968442482</v>
+        <v>0.0001692524614766709</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R152" t="b">
         <v>0</v>
@@ -10091,10 +10091,10 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0.0004186430593685542</v>
+        <v>6.630103706080571e-05</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.01668741237731318</v>
+        <v>0.01377606248960877</v>
       </c>
       <c r="R153" t="b">
         <v>0</v>
